--- a/output/2026-10-06_19_Croazia_Grad_Zagreb_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-06_19_Croazia_Grad_Zagreb_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -474,7 +474,6 @@
           <t>Trgostal-Lubenjak d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Kovinska 4a, 10090 Zagreb - Grad Zagreb</t>
@@ -485,11 +484,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore di macchine e utensili per lavorazione metalli (seghe a nastro, piegatubi/profilatrici, macchine taglio laser/gas/acqua, presse piegatrici, utensileria elettrica/pneumatica; oltre 300.000 utensili di 900+ marchi). Esistenza confermata tramite automa.net e documenti giudiziari che citano la sede in Kovinska 4a. Nessun sito web ufficiale individuato con certezza; telefono ed email non reperiti da fonte verificabile, pertanto lasciati vuoti.</t>
+          <t>Distributore di macchine e utensili per lavorazione metalli (seghe a nastro, piegatubi/profilatrici, macchine taglio laser/gas/acqua, presse piegatrici, utensileria elettrica/pneumatica; oltre 300.000 utensili di 900+ marchi). Esistenza confermata tramite automa.net e documenti giudiziari che citano la sede in Kovinska 4a. Nessun sito web ufficiale individuato con certezza; telefono ed email non reperiti da fonte verificabile, pertanto lasciati vuoti. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -531,7 +528,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Importatore e rivenditore di macchine utensili CNC, software correlati, utensili da taglio e accessori; formazione tecnologica e demo center. Confermata tramite companywall.hr, fininfo e sito ufficiale (66 dipendenti, direttore Stipo Marić).</t>
+          <t>Importatore e rivenditore di macchine utensili CNC, software correlati, utensili da taglio e accessori; formazione tecnologica e demo center. Confermata tramite companywall.hr, fininfo e sito ufficiale (66 dipendenti, direttore Stipo Marić). [DUPLICATO — vedi anche: 2026-10-06_17_Croazia_Grad_Zagreb_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -546,7 +543,6 @@
           <t>Teximp d.o.o. (Haas Factory Outlet / HFO Croazia)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Rimski put 31, 10360 Sesvete, Zagreb - Grad Zagreb</t>
@@ -557,8 +553,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore/centro tecnologico-assistenza per macchine utensili CNC, rappresentante esclusivo Haas Automation in Croazia; appartiene al gruppo internazionale Teximp (Zurigo/Texim Europe). Esistenza confermata da machinetools.com, lider.media e pagine Haas CNC (HFO Bosnia/Slovenia citano la rete Teximp). Sito/telefono/email ufficiali della sede croata non reperiti con certezza, lasciati vuoti.</t>
@@ -576,7 +570,6 @@
           <t>Lorsel Strojevi d.o.o. (Lorsel Group)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Industrijska ulica 15, 10290 Zaprešić - Zagrebačka županija (area metropolitana Zagabria)</t>
@@ -587,8 +580,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda di consulenza e vendita macchine/utensili/attrezzature per lavorazione lamiera (taglio ad acqua, piegatrici servo-elettriche, raddrizzatrici, sbavatrici, calandre); partner esclusivo Worcon per Croazia/BiH/Serbia. Confermata da blog.wor-con.com e blechexpo-messe.de (espositore fiera). Telefono/email rinvenuti solo su fonti di scarsa affidabilità (prospeo.io con formato email generico non verificato), pertanto non riportati per non rischiare dati inventati.</t>
@@ -633,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Grossista/distributore di attrezzature, utensili e materiali per industria (energia, ferrovie, industria generale); certificata ISO 9001/14001. Dati confermati tramite WebFetch del sito ufficiale (pagina Contatti/About us).</t>
+          <t>Grossista/distributore di attrezzature, utensili e materiali per industria (energia, ferrovie, industria generale); certificata ISO 9001/14001. Dati confermati tramite WebFetch del sito ufficiale (pagina Contatti/About us). [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -675,7 +666,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leader in Croazia per filtrazione/ventilazione industriale: sistemi di depolverazione, cabine di verniciatura, trasporto pneumatico (applicabile anche a metalworking). Dati confermati via WebFetch del sito ufficiale, che riporta email generica info@ (diversa da quella HR indicata nella lista grezza).</t>
+          <t>Leader in Croazia per filtrazione/ventilazione industriale: sistemi di depolverazione, cabine di verniciatura, trasporto pneumatico (applicabile anche a metalworking). Dati confermati via WebFetch del sito ufficiale, che riporta email generica info@ (diversa da quella HR indicata nella lista grezza). [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -710,7 +701,6 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Distributore mecatronica, pneumatica, idraulica, automazione, trattamento acque; Premium Partner Filtration Group Industrial per filtrazione aria industriale. Sede e telefono confermati via WebFetch del sito ufficiale; l'indirizzo email generico risultava oscurato/non leggibile nella pagina e non è stato reperito da altra fonte verificabile, quindi lasciato vuoto.</t>

--- a/output/2026-10-06_19_Croazia_Grad_Zagreb_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-06_19_Croazia_Grad_Zagreb_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
